--- a/Machine Data.xlsx
+++ b/Machine Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="WJ" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -594,6 +594,94 @@
         <v>28</v>
       </c>
       <c r="C29">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40">
         <v>699</v>
       </c>
     </row>
